--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/GANDAKI_Datenbank/before_conversion_gandaki_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/GANDAKI_Datenbank/before_conversion_gandaki_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="79">
   <si>
     <t>location</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>Database_number</t>
+  </si>
+  <si>
+    <t>Database_name</t>
   </si>
   <si>
     <t>Bahun Danda, Lamjung</t>
@@ -611,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD13"/>
+  <dimension ref="A1:AE13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -639,9 +642,10 @@
     <col min="28" max="28" width="18.7109375" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" customWidth="1"/>
     <col min="30" max="30" width="17.7109375" customWidth="1"/>
+    <col min="31" max="31" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -732,13 +736,16 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" spans="1:30">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2">
         <v>28.34135</v>
@@ -768,7 +775,7 @@
         <v>3963.64</v>
       </c>
       <c r="R2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S2">
         <v>173.33</v>
@@ -777,24 +784,24 @@
         <v>136.7</v>
       </c>
       <c r="X2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Z2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AA2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AD2">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3">
         <v>28.41303</v>
@@ -824,7 +831,7 @@
         <v>514.92</v>
       </c>
       <c r="R3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S3">
         <v>73.33</v>
@@ -833,24 +840,24 @@
         <v>13.2</v>
       </c>
       <c r="X3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Z3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AA3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD3">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4">
         <v>28.55369</v>
@@ -880,7 +887,7 @@
         <v>761.51</v>
       </c>
       <c r="R4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="S4">
         <v>80</v>
@@ -889,24 +896,24 @@
         <v>33.4</v>
       </c>
       <c r="X4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AA4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AD4">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5">
         <v>28.30561</v>
@@ -936,7 +943,7 @@
         <v>1184.21</v>
       </c>
       <c r="R5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S5">
         <v>490</v>
@@ -945,24 +952,24 @@
         <v>49.6</v>
       </c>
       <c r="X5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Z5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AA5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD5">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C6">
         <v>28.42176</v>
@@ -992,7 +999,7 @@
         <v>34.58</v>
       </c>
       <c r="R6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S6">
         <v>192</v>
@@ -1001,24 +1008,24 @@
         <v>7.7</v>
       </c>
       <c r="X6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AA6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AD6">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7">
         <v>28.4594</v>
@@ -1048,7 +1055,7 @@
         <v>56.99</v>
       </c>
       <c r="R7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S7">
         <v>80</v>
@@ -1057,24 +1064,24 @@
         <v>5.6</v>
       </c>
       <c r="X7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AD7">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C8">
         <v>28.47828</v>
@@ -1104,7 +1111,7 @@
         <v>34.58</v>
       </c>
       <c r="R8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S8">
         <v>108</v>
@@ -1113,24 +1120,24 @@
         <v>5.1</v>
       </c>
       <c r="X8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AA8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AD8">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:31">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C9">
         <v>28.49626</v>
@@ -1160,7 +1167,7 @@
         <v>412.45</v>
       </c>
       <c r="R9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S9">
         <v>190</v>
@@ -1169,24 +1176,24 @@
         <v>39.4</v>
       </c>
       <c r="X9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA9" t="s">
         <v>69</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>68</v>
       </c>
       <c r="AD9">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:31">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C10">
         <v>28.45786</v>
@@ -1216,7 +1223,7 @@
         <v>229.62</v>
       </c>
       <c r="R10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S10">
         <v>313.33</v>
@@ -1225,24 +1232,24 @@
         <v>70.09999999999999</v>
       </c>
       <c r="X10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AA10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD10">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C11">
         <v>28.45316</v>
@@ -1272,7 +1279,7 @@
         <v>28.17</v>
       </c>
       <c r="R11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S11">
         <v>61.33</v>
@@ -1281,24 +1288,24 @@
         <v>2.8</v>
       </c>
       <c r="X11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AA11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AD11">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:31">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C12">
         <v>28.45316</v>
@@ -1328,7 +1335,7 @@
         <v>28.17</v>
       </c>
       <c r="R12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S12">
         <v>61.33</v>
@@ -1337,24 +1344,24 @@
         <v>3.4</v>
       </c>
       <c r="X12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AA12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AD12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:31">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C13">
         <v>28.36776</v>
@@ -1384,7 +1391,7 @@
         <v>450.88</v>
       </c>
       <c r="R13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="S13">
         <v>390</v>
@@ -1393,13 +1400,13 @@
         <v>32.2</v>
       </c>
       <c r="X13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Z13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AA13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AD13">
         <v>11</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/GANDAKI_Datenbank/before_conversion_gandaki_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/GANDAKI_Datenbank/before_conversion_gandaki_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="80">
   <si>
     <t>location</t>
   </si>
@@ -179,6 +179,9 @@
   </si>
   <si>
     <t>S12</t>
+  </si>
+  <si>
+    <t>Metamorphic Rock</t>
   </si>
   <si>
     <t>9.2</t>
@@ -622,7 +625,7 @@
     <col min="3" max="3" width="16.7109375" customWidth="1"/>
     <col min="4" max="4" width="17.7109375" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
     <col min="7" max="7" width="22.7109375" customWidth="1"/>
     <col min="8" max="8" width="18.7109375" customWidth="1"/>
     <col min="9" max="9" width="38.7109375" customWidth="1"/>
@@ -753,6 +756,9 @@
       <c r="D2">
         <v>84.40621</v>
       </c>
+      <c r="F2" t="s">
+        <v>55</v>
+      </c>
       <c r="H2">
         <v>47.1</v>
       </c>
@@ -775,7 +781,7 @@
         <v>3963.64</v>
       </c>
       <c r="R2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S2">
         <v>173.33</v>
@@ -784,13 +790,13 @@
         <v>136.7</v>
       </c>
       <c r="X2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Z2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AA2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AD2">
         <v>11</v>
@@ -809,6 +815,9 @@
       <c r="D3">
         <v>84.40649000000001</v>
       </c>
+      <c r="F3" t="s">
+        <v>55</v>
+      </c>
       <c r="H3">
         <v>36.6</v>
       </c>
@@ -831,7 +840,7 @@
         <v>514.92</v>
       </c>
       <c r="R3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="S3">
         <v>73.33</v>
@@ -840,13 +849,13 @@
         <v>13.2</v>
       </c>
       <c r="X3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AD3">
         <v>11</v>
@@ -865,6 +874,9 @@
       <c r="D4">
         <v>84.25097</v>
       </c>
+      <c r="F4" t="s">
+        <v>55</v>
+      </c>
       <c r="H4">
         <v>57</v>
       </c>
@@ -887,7 +899,7 @@
         <v>761.51</v>
       </c>
       <c r="R4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S4">
         <v>80</v>
@@ -896,13 +908,13 @@
         <v>33.4</v>
       </c>
       <c r="X4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Z4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AA4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD4">
         <v>11</v>
@@ -921,6 +933,9 @@
       <c r="D5">
         <v>83.94889999999999</v>
       </c>
+      <c r="F5" t="s">
+        <v>55</v>
+      </c>
       <c r="H5">
         <v>31.6</v>
       </c>
@@ -943,7 +958,7 @@
         <v>1184.21</v>
       </c>
       <c r="R5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S5">
         <v>490</v>
@@ -952,13 +967,13 @@
         <v>49.6</v>
       </c>
       <c r="X5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Z5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AA5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD5">
         <v>11</v>
@@ -977,6 +992,9 @@
       <c r="D6">
         <v>83.82062000000001</v>
       </c>
+      <c r="F6" t="s">
+        <v>55</v>
+      </c>
       <c r="H6">
         <v>40.1</v>
       </c>
@@ -999,7 +1017,7 @@
         <v>34.58</v>
       </c>
       <c r="R6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S6">
         <v>192</v>
@@ -1008,13 +1026,13 @@
         <v>7.7</v>
       </c>
       <c r="X6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Z6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AA6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AD6">
         <v>11</v>
@@ -1033,6 +1051,9 @@
       <c r="D7">
         <v>83.62718</v>
       </c>
+      <c r="F7" t="s">
+        <v>55</v>
+      </c>
       <c r="H7">
         <v>53.9</v>
       </c>
@@ -1055,7 +1076,7 @@
         <v>56.99</v>
       </c>
       <c r="R7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S7">
         <v>80</v>
@@ -1064,13 +1085,13 @@
         <v>5.6</v>
       </c>
       <c r="X7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Z7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AA7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD7">
         <v>11</v>
@@ -1089,6 +1110,9 @@
       <c r="D8">
         <v>83.64129</v>
       </c>
+      <c r="F8" t="s">
+        <v>55</v>
+      </c>
       <c r="H8">
         <v>54.4</v>
       </c>
@@ -1111,7 +1135,7 @@
         <v>34.58</v>
       </c>
       <c r="R8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S8">
         <v>108</v>
@@ -1120,13 +1144,13 @@
         <v>5.1</v>
       </c>
       <c r="X8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Z8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AA8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AD8">
         <v>11</v>
@@ -1145,6 +1169,9 @@
       <c r="D9">
         <v>83.65428</v>
       </c>
+      <c r="F9" t="s">
+        <v>55</v>
+      </c>
       <c r="H9">
         <v>62.8</v>
       </c>
@@ -1167,7 +1194,7 @@
         <v>412.45</v>
       </c>
       <c r="R9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S9">
         <v>190</v>
@@ -1176,13 +1203,13 @@
         <v>39.4</v>
       </c>
       <c r="X9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Z9" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA9" t="s">
         <v>70</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>69</v>
       </c>
       <c r="AD9">
         <v>11</v>
@@ -1201,6 +1228,9 @@
       <c r="D10">
         <v>83.62614000000001</v>
       </c>
+      <c r="F10" t="s">
+        <v>55</v>
+      </c>
       <c r="H10">
         <v>64.3</v>
       </c>
@@ -1223,7 +1253,7 @@
         <v>229.62</v>
       </c>
       <c r="R10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S10">
         <v>313.33</v>
@@ -1232,13 +1262,13 @@
         <v>70.09999999999999</v>
       </c>
       <c r="X10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Z10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AA10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD10">
         <v>11</v>
@@ -1257,6 +1287,9 @@
       <c r="D11">
         <v>83.51419</v>
       </c>
+      <c r="F11" t="s">
+        <v>55</v>
+      </c>
       <c r="H11">
         <v>52.7</v>
       </c>
@@ -1279,7 +1312,7 @@
         <v>28.17</v>
       </c>
       <c r="R11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S11">
         <v>61.33</v>
@@ -1288,13 +1321,13 @@
         <v>2.8</v>
       </c>
       <c r="X11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Z11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AA11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AD11">
         <v>11</v>
@@ -1313,6 +1346,9 @@
       <c r="D12">
         <v>83.51419</v>
       </c>
+      <c r="F12" t="s">
+        <v>55</v>
+      </c>
       <c r="H12">
         <v>47.9</v>
       </c>
@@ -1335,7 +1371,7 @@
         <v>28.17</v>
       </c>
       <c r="R12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S12">
         <v>61.33</v>
@@ -1344,13 +1380,13 @@
         <v>3.4</v>
       </c>
       <c r="X12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Z12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AA12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AD12">
         <v>11</v>
@@ -1369,6 +1405,9 @@
       <c r="D13">
         <v>83.5025</v>
       </c>
+      <c r="F13" t="s">
+        <v>55</v>
+      </c>
       <c r="H13">
         <v>52.5</v>
       </c>
@@ -1391,7 +1430,7 @@
         <v>450.88</v>
       </c>
       <c r="R13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S13">
         <v>390</v>
@@ -1400,13 +1439,13 @@
         <v>32.2</v>
       </c>
       <c r="X13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AA13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AD13">
         <v>11</v>
